--- a/data/Run_Game.xlsx
+++ b/data/Run_Game.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wopi.dropbox.com/wopi/files/oid_2066026440720268800/WOPIServiceId_TP_DROPBOX_PLUS/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="332" documentId="13_ncr:40001_{302A552D-BD55-4259-865D-12213D42E890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82A90EF9-7BBF-4919-925F-D8FDD6E7547A}"/>
+  <xr:revisionPtr revIDLastSave="370" documentId="13_ncr:40001_{302A552D-BD55-4259-865D-12213D42E890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C49B223-38AF-4277-BC8D-7C5CA47860DA}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25320" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Run game" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>Number of depositors</t>
   </si>
@@ -73,10 +73,6 @@
 (= Leaving depositors x 100)</t>
   </si>
   <si>
-    <t>Book value of remaining assets
-(Initial assets - Assets sold)</t>
-  </si>
-  <si>
     <t>AT MATURITY</t>
   </si>
   <si>
@@ -99,6 +95,14 @@
   </si>
   <si>
     <t>Equity</t>
+  </si>
+  <si>
+    <t>Remaining deposits
+(=Staying depositors x100)</t>
+  </si>
+  <si>
+    <t>Remaining assets
+(=Initial assets - Assets sold)</t>
   </si>
 </sst>
 </file>
@@ -114,7 +118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,6 +128,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -230,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -254,12 +264,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -273,6 +277,33 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,64 +618,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01703846-CDCD-4A93-B07C-4D347637CB70}">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3">
         <v>0.02</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="24"/>
+      <c r="D6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="11"/>
+      <c r="F6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="13"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G6" s="11"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="C7" s="8"/>
       <c r="D7" s="6" t="s">
@@ -662,23 +694,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B10" s="24"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -687,7 +720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -695,8 +728,12 @@
         <f>B11*100</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>9</v>
       </c>
@@ -704,118 +741,111 @@
         <f>B13/B3</f>
         <v>0</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+    </row>
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <f>E7-B14</f>
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+    </row>
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <f>B10*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19">
+        <f>B15*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E15" s="5">
-        <f>B15</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="5">
-        <f>B10*100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-    </row>
-    <row r="20" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E19" s="18"/>
+      <c r="F19" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B20">
-        <f>B15*1.05</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="12" t="s">
+        <f>B16*1.02</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E20" s="21">
+        <f>B19</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="21">
+        <f>B20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B21">
-        <f>G15*1.02</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="10">
-        <f>B20</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G21" s="10">
+        <f>B19-B20</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="23">
         <f>B21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22">
-        <f>B20-B21</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G22" s="5">
-        <f>B22</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
+  <mergeCells count="7">
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
